--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/INDIANA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/INDIANA_2010.xlsx
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C162">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C608">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C662">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C686">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C959">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1101">
